--- a/stories/arbres/TREE-COL-016.xlsx
+++ b/stories/arbres/TREE-COL-016.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Iris arrive en classe avec maman. Elle s'assoit. La maîtresse pose une question. Iris lève la main. Il faut attendre. Puis elle pourra parler.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sur le tapis, Iris lève la main. Elle attend. Puis elle parle. Elle dit : le tapis est doux.</t>
+          <t>Sur le tapis, Iris lève la main. Elle attend. Puis elle parle. Le tapis est doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le tapis, Iris lève la main. Elle attend. Puis elle parle.
+narrateur|Le tapis est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le tapis, que fait Iris d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Iris a attendu. Puis elle a parlé.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire commence. Iris attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|On chante. Iris attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Iris dessine. Elle attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À la table, Iris lève la main. Elle attend. Puis elle parle. Elle dit : la table est lisse.</t>
+          <t>À la table, Iris lève la main. Elle attend. Puis elle parle. La table est lisse.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, Iris lève la main. Elle attend. Puis elle parle.
+narrateur|La table est lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, que fait Iris d'abord ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Attendre, puis parler.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, l'histoire. Iris attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|La chanson à la table. Iris attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Le dessin à la table. Iris attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, Iris lève la main. Elle attend. Puis elle parle. Elle dit : je vois un oiseau.</t>
+          <t>Près de la fenêtre, Iris lève la main. Elle attend. Puis elle parle. Je vois un oiseau.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la fenêtre, Iris lève la main. Elle attend. Puis elle parle.
+narrateur|Je vois un oiseau.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la fenêtre, que fait Iris d'abord ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la fenêtre, l'histoire. Iris attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|On chante près de la lumière. Iris attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Iris dessine la fenêtre. Elle attend. Puis elle parle.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-016.xlsx
+++ b/stories/arbres/TREE-COL-016.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Iris arrive en classe avec maman. Elle s'assoit. La maîtresse pose une question. Iris lève la main. Il faut attendre. Puis elle pourra parler.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 narrateur|Le tapis est doux.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Sur le tapis, que fait Iris d'abord ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Iris a attendu. Puis elle a parlé.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|L'histoire commence. Iris attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|On chante. Iris attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Iris dessine. Elle attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 narrateur|La table est lisse.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|À la table, que fait Iris d'abord ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Attendre, puis parler.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|À la table, l'histoire. Iris attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|La chanson à la table. Iris attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Le dessin à la table. Iris attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 narrateur|Je vois un oiseau.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Près de la fenêtre, que fait Iris d'abord ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Près de la fenêtre, l'histoire. Iris attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|On chante près de la lumière. Iris attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Iris dessine la fenêtre. Elle attend. Puis elle parle.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-016.xlsx
+++ b/stories/arbres/TREE-COL-016.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iris attend puis parle</t>
+          <t>La craie et l'oiseau de Victorina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sur le carton, une craie jaune. Dehors, un oiseau sous la pluie. Victorina veut le dire, dans la petite classe. Elle lève la main, elle attend, puis elle parle, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris arrive en classe avec maman. Elle s'assoit. La maîtresse pose une question. Iris lève la main. Il faut attendre. Puis elle pourra parler.</t>
+          <t>Un carton est collé contre le buffet. Un trait de craie jaune y reste. La lampe fait un rond chaud. La pluie tape la vitre, tout doux. Un oiseau jaune s'est posé dehors. Ses pattes tiennent le rebord. La soupe mijote, tout loin, dans la cuisine. Maman a mis trois coussins par terre. C'est notre petite classe, Victorina. Tu as vu l'oiseau ? Il est jaune. En ce moment, Victorina s'assoit. Le carton est un tableau, tout simple. Elle a une chose à dire. Maman parle encore de la pluie. Victorina lève la main. Elle attend. On lève la main. On attend. Puis on parle. C'est bientôt ton tour. L'oiseau est sur le rebord. Bravo. Tu as attendu. La craie jaune laisse un peu de poussière. L'oiseau penche la tête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,39 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Iris arrive en classe avec maman. Elle s'assoit. La maîtresse pose une question. Iris lève la main. Il faut attendre. Puis elle pourra parler.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un carton est collé contre le buffet.
+narrateur|Un trait de craie jaune y reste.
+narrateur|La lampe fait un rond chaud.
+narrateur|La pluie tape la vitre, tout doux.
+narrateur|Un oiseau jaune s'est posé dehors.
+narrateur|Ses pattes tiennent le rebord.
+narrateur|La soupe mijote, tout loin, dans la cuisine.
+narrateur|Maman a mis trois coussins par terre.
+papa|C'est notre petite classe, Victorina.
+maman|Tu as vu l'oiseau ?
+enfant-f|Il est jaune.
+narrateur|En ce moment, Victorina s'assoit.
+narrateur|Le carton est un tableau, tout simple.
+narrateur|Elle a une chose à dire.
+narrateur|Maman parle encore de la pluie.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+maman|C'est bientôt ton tour.
+enfant-f|L'oiseau est sur le rebord.
+maman|Bravo.
+maman|Tu as attendu.
+narrateur|La craie jaune laisse un peu de poussière.
+narrateur|L'oiseau penche la tête.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie,craie</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1394,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le tapis, la table, ou la fenêtre.</t>
+          <t>Où s'assoit Victorina ? Le tapis, la table, ou la fenêtre ? On s'écoute. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1558,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le tapis, la table, ou la fenêtre.</t>
+          <t>narrateur|Où s'assoit Victorina ?
+maman|Le tapis, la table, ou la fenêtre ?
+papa|On s'écoute.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sur le tapis, Iris lève la main. Elle attend. Puis elle parle. Le tapis est doux.</t>
+          <t>Victorina s'assoit sur le tapis. Le tapis est épais, un peu rêche. Un fil rouge dépasse, tout doux. La poussière de craie brille un peu. Moi, je raconte le tapis d'abord. Maman parle jusqu'au bout. Victorina a une chose à dire. Elle lève la main. Elle attend. L'oiseau est jaune, dehors. Oui. C'est ton tour. Tu as attendu. On lève la main. On attend. Puis on parle. Victorina pose la paume sur le tapis. Le fil rouge chatouille le poignet.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1730,30 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sur le tapis, Iris lève la main. Elle attend. Puis elle parle.
-narrateur|Le tapis est doux.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina s'assoit sur le tapis.
+narrateur|Le tapis est épais, un peu rêche.
+narrateur|Un fil rouge dépasse, tout doux.
+narrateur|La poussière de craie brille un peu.
+maman|Moi, je raconte le tapis d'abord.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Victorina a une chose à dire.
+narrateur|Elle lève la main.
+narrateur|Elle attend.
+enfant-f|L'oiseau est jaune, dehors.
+papa|Oui. C'est ton tour.
+papa|Tu as attendu.
+maman|On lève la main.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Victorina pose la paume sur le tapis.
+narrateur|Le fil rouge chatouille le poignet.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>tapis</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sur le tapis, que fait Iris d'abord ?</t>
+          <t>Sur le tapis, Victorina veut parler. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1870,7 +1934,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sur le tapis, que fait Iris d'abord ?</t>
+          <t>narrateur|Sur le tapis, Victorina veut parler.
+maman|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1898,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Iris a attendu. Puis elle a parlé.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Victorina souffle un peu. Sa main redescend, tout doux. J'ai attendu. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2107,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Iris a attendu. Puis elle a parlé.</t>
+          <t>maman|Oui.
+maman|On lève la main.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Victorina souffle un peu.
+narrateur|Sa main redescend, tout doux.
+enfant-f|J'ai attendu.
+papa|Bravo.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2143,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>La petite classe a trois jeux. L'histoire, la chanson, ou le dessin ? On écoute. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2307,11 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|La petite classe a trois jeux.
+maman|L'histoire, la chanson, ou le dessin ?
+papa|On écoute.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2339,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>L'histoire commence. Iris attend. Puis elle parle.</t>
+          <t>Maman ouvre un livre d'images. Une page sent le papier, un peu sec. Un oiseau y est dessiné, tout jaune. Moi, je lis l'histoire d'abord. Maman lit jusqu'au bout. Victorina lève la main. Elle attend. C'est ton tour. Le mien est dehors, sur le rebord. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorina pose un doigt sur l'image. Le livre repose sur le tapis, tout ouvert. On est encore sur le tapis. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,10 +2479,30 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire commence. Iris attend. Puis elle parle.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Maman ouvre un livre d'images.
+narrateur|Une page sent le papier, un peu sec.
+narrateur|Un oiseau y est dessiné, tout jaune.
+maman|Moi, je lis l'histoire d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour.
+enfant-f|Le mien est dehors, sur le rebord.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorina pose un doigt sur l'image.
+narrateur|Le livre repose sur le tapis, tout ouvert.
+narrateur|On est encore sur le tapis.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2430,7 +2527,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2695,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2726,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, sur le tapis. La poupée a le livre contre les genoux. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,7 +2866,22 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, sur le tapis.
+narrateur|La poupée a le livre contre les genoux.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2794,7 +2909,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, sur le tapis. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3049,14 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, sur le tapis.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3084,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, sur le tapis. L'ours pose le nez sur une page. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3224,22 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, sur le tapis.
+narrateur|L'ours pose le nez sur une page.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3267,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, sur le tapis. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3407,14 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, sur le tapis.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3442,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, sur le tapis. Le lion écoute l'histoire, tout sage. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,7 +3582,22 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant l'histoire.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, sur le tapis.
+narrateur|Le lion écoute l'histoire, tout sage.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3466,7 +3625,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, sur le tapis. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3765,14 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, sur le tapis.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3800,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>On chante. Iris attend. Puis elle parle.</t>
+          <t>Papa tapote la table, tout léger. Une chanson de pluie commence. Les gouttes suivent le rythme, dehors. Moi, je chante d'abord. Papa chante jusqu'au bout. Victorina lève la main. Elle attend. Je peux chanter l'oiseau ? Oui. C'est ton tour. On a attendu. Puis on parle. Victorina chante tout bas, tout doux. Bravo, Victorina. Le fil rouge du tapis suit la chanson. On est encore sur le tapis. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,7 +3940,23 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|On chante. Iris attend. Puis elle parle.</t>
+          <t>narrateur|Papa tapote la table, tout léger.
+narrateur|Une chanson de pluie commence.
+narrateur|Les gouttes suivent le rythme, dehors.
+papa|Moi, je chante d'abord.
+narrateur|Papa chante jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Je peux chanter l'oiseau ?
+maman|Oui. C'est ton tour.
+maman|On a attendu.
+maman|Puis on parle.
+narrateur|Victorina chante tout bas, tout doux.
+papa|Bravo, Victorina.
+narrateur|Le fil rouge du tapis suit la chanson.
+narrateur|On est encore sur le tapis.
+maman|On attend.
+maman|Puis on parle.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3802,7 +3984,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3970,7 +4152,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3998,7 +4183,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, sur le tapis. La poupée balance un peu, au rythme. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4138,7 +4323,22 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, sur le tapis.
+narrateur|La poupée balance un peu, au rythme.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4166,7 +4366,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, sur le tapis. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4306,7 +4506,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, sur le tapis.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4334,7 +4541,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, sur le tapis. L'ours tape l'oreille, tout doux. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4474,7 +4681,22 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, sur le tapis.
+narrateur|L'ours tape l'oreille, tout doux.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4502,7 +4724,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, sur le tapis. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4642,7 +4864,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, sur le tapis.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4670,7 +4899,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, sur le tapis. La crinière tremble, comme un refrain. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4810,7 +5039,22 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant la chanson.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, sur le tapis.
+narrateur|La crinière tremble, comme un refrain.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4838,7 +5082,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, sur le tapis. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4978,7 +5222,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, sur le tapis.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5006,7 +5257,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Iris dessine. Elle attend. Puis elle parle.</t>
+          <t>Victorina prend un morceau de craie. La craie est jaune, un peu cassée. Elle fait un bruit rêche sur le carton. Moi, je dessine d'abord un nuage. Maman dessine jusqu'au bout. Victorina lève la main. Elle attend. Un bec, et deux pattes ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Un petit oiseau jaune apparaît. Un peu de craie tombe sur le tapis. On est encore sur le tapis. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5146,10 +5397,31 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Iris dessine. Elle attend. Puis elle parle.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Victorina prend un morceau de craie.
+narrateur|La craie est jaune, un peu cassée.
+narrateur|Elle fait un bruit rêche sur le carton.
+maman|Moi, je dessine d'abord un nuage.
+narrateur|Maman dessine jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Un bec, et deux pattes ?
+papa|Oui. C'est ton tour.
+papa|On attend.
+papa|Puis on parle.
+maman|Bravo.
+maman|Tu as attendu ton tour.
+narrateur|Un petit oiseau jaune apparaît.
+narrateur|Un peu de craie tombe sur le tapis.
+narrateur|On est encore sur le tapis.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5174,7 +5446,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5342,7 +5614,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5370,7 +5645,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, sur le tapis. Un point de craie tache la robe. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5510,7 +5785,22 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, sur le tapis.
+narrateur|Un point de craie tache la robe.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5538,7 +5828,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, sur le tapis. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5678,7 +5968,14 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, sur le tapis.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5706,7 +6003,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, sur le tapis. L'ours a un trait jaune sur le ventre. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5846,7 +6143,22 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, sur le tapis.
+narrateur|L'ours a un trait jaune sur le ventre.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5874,7 +6186,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, sur le tapis. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6014,7 +6326,14 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, sur le tapis.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6042,7 +6361,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, sur le tapis. Une mèche de laine a un peu de craie. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6182,7 +6501,22 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à le tapis, pendant le dessin.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, sur le tapis.
+narrateur|Une mèche de laine a un peu de craie.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6210,7 +6544,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, sur le tapis. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6350,7 +6684,14 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, sur le tapis.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6378,7 +6719,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À la table, Iris lève la main. Elle attend. Puis elle parle. La table est lisse.</t>
+          <t>Victorina s'assoit à la table. Le bois est lisse, un peu froid. Le carton-tableau est collé tout près. Un trait de craie jaune y tremble. Moi, je raconte le carton. Papa parle, tout calme. Victorina lève la main. Elle attend. La craie fait un oiseau. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorina pose un doigt sur le bois. La lampe fait un rond chaud. Bravo, Victorina. Tu as levé la main.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6518,11 +6859,29 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|À la table, Iris lève la main. Elle attend. Puis elle parle.
-narrateur|La table est lisse.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Victorina s'assoit à la table.
+narrateur|Le bois est lisse, un peu froid.
+narrateur|Le carton-tableau est collé tout près.
+narrateur|Un trait de craie jaune y tremble.
+papa|Moi, je raconte le carton.
+narrateur|Papa parle, tout calme.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|La craie fait un oiseau.
+maman|Oui. Merci d'avoir attendu.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Victorina pose un doigt sur le bois.
+narrateur|La lampe fait un rond chaud.
+papa|Bravo, Victorina.
+papa|Tu as levé la main.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6547,7 +6906,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>À la table, que fait Iris d'abord ?</t>
+          <t>À la table, Victorina lève la main. Et après, on attend ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6703,7 +7062,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|À la table, que fait Iris d'abord ?</t>
+          <t>narrateur|À la table, Victorina lève la main.
+papa|Et après, on attend ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6731,7 +7091,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Attendre, puis parler.</t>
+          <t>Oui. On attend. Puis on parle. Victorina essuie un peu de craie. J'attends mon tour. Bravo, Victorina. La table est à toi, et le tour aussi.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6875,7 +7235,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Attendre, puis parler.</t>
+          <t>papa|Oui.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorina essuie un peu de craie.
+enfant-f|J'attends mon tour.
+maman|Bravo, Victorina.
+maman|La table est à toi, et le tour aussi.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6903,7 +7269,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>La petite classe a trois jeux. L'histoire, la chanson, ou le dessin ? On écoute. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7067,7 +7433,11 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|La petite classe a trois jeux.
+maman|L'histoire, la chanson, ou le dessin ?
+papa|On écoute.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7095,7 +7465,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>À la table, l'histoire. Iris attend. Puis elle parle.</t>
+          <t>Maman ouvre un livre d'images. Une page sent le papier, un peu sec. Un oiseau y est dessiné, tout jaune. Moi, je lis l'histoire d'abord. Maman lit jusqu'au bout. Victorina lève la main. Elle attend. C'est ton tour. Le mien est dehors, sur le rebord. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorina pose un doigt sur l'image. Le livre est collé contre le carton. On est encore à la table. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7235,10 +7605,30 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|À la table, l'histoire. Iris attend. Puis elle parle.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Maman ouvre un livre d'images.
+narrateur|Une page sent le papier, un peu sec.
+narrateur|Un oiseau y est dessiné, tout jaune.
+maman|Moi, je lis l'histoire d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour.
+enfant-f|Le mien est dehors, sur le rebord.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorina pose un doigt sur l'image.
+narrateur|Le livre est collé contre le carton.
+narrateur|On est encore à la table.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,7 +7653,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7431,7 +7821,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7459,7 +7852,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, à la table. La poupée est assise contre le carton. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7599,7 +7992,22 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, à la table.
+narrateur|La poupée est assise contre le carton.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7627,7 +8035,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, à la table. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7767,7 +8175,14 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, à la table.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7795,7 +8210,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, à la table. L'ours tient le livre, tout maladroit. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7935,7 +8350,22 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, à la table.
+narrateur|L'ours tient le livre, tout maladroit.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7963,7 +8393,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, à la table. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8103,7 +8533,14 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, à la table.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8131,7 +8568,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, à la table. Le lion garde la page avec la patte. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8271,7 +8708,22 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant l'histoire.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, à la table.
+narrateur|Le lion garde la page avec la patte.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8299,7 +8751,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, à la table. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8439,7 +8891,14 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, à la table.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8467,7 +8926,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>La chanson à la table. Iris attend. Puis elle parle.</t>
+          <t>Papa tapote la table, tout léger. Une chanson de pluie commence. Les gouttes suivent le rythme, dehors. Moi, je chante d'abord. Papa chante jusqu'au bout. Victorina lève la main. Elle attend. Je peux chanter l'oiseau ? Oui. C'est ton tour. On a attendu. Puis on parle. Victorina chante tout bas, tout doux. Bravo, Victorina. La table vibre un peu, sous les doigts. On est encore à la table. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8607,7 +9066,23 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|La chanson à la table. Iris attend. Puis elle parle.</t>
+          <t>narrateur|Papa tapote la table, tout léger.
+narrateur|Une chanson de pluie commence.
+narrateur|Les gouttes suivent le rythme, dehors.
+papa|Moi, je chante d'abord.
+narrateur|Papa chante jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Je peux chanter l'oiseau ?
+maman|Oui. C'est ton tour.
+maman|On a attendu.
+maman|Puis on parle.
+narrateur|Victorina chante tout bas, tout doux.
+papa|Bravo, Victorina.
+narrateur|La table vibre un peu, sous les doigts.
+narrateur|On est encore à la table.
+maman|On attend.
+maman|Puis on parle.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8635,7 +9110,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8803,7 +9278,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8831,7 +9309,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, à la table. La poupée a un ticket de papier, tout plié. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8971,7 +9449,22 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, à la table.
+narrateur|La poupée a un ticket de papier, tout plié.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -8999,7 +9492,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, à la table. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9139,7 +9632,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, à la table.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9167,7 +9667,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, à la table. L'ours tapote le bois, avec papa. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9307,7 +9807,22 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, à la table.
+narrateur|L'ours tapote le bois, avec papa.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9335,7 +9850,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, à la table. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9475,7 +9990,14 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, à la table.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9503,7 +10025,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, à la table. Le lion fait un tout petit rrr, au refrain. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9643,7 +10165,22 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant la chanson.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, à la table.
+narrateur|Le lion fait un tout petit rrr, au refrain.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9671,7 +10208,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, à la table. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9811,7 +10348,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, à la table.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9839,7 +10383,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Le dessin à la table. Iris attend. Puis elle parle.</t>
+          <t>Victorina prend un morceau de craie. La craie est jaune, un peu cassée. Elle fait un bruit rêche sur le carton. Moi, je dessine d'abord un nuage. Maman dessine jusqu'au bout. Victorina lève la main. Elle attend. Un bec, et deux pattes ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Un petit oiseau jaune apparaît. La craie laisse une poussière sur le bois. On est encore à la table. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9979,10 +10523,31 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Le dessin à la table. Iris attend. Puis elle parle.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Victorina prend un morceau de craie.
+narrateur|La craie est jaune, un peu cassée.
+narrateur|Elle fait un bruit rêche sur le carton.
+maman|Moi, je dessine d'abord un nuage.
+narrateur|Maman dessine jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Un bec, et deux pattes ?
+papa|Oui. C'est ton tour.
+papa|On attend.
+papa|Puis on parle.
+maman|Bravo.
+maman|Tu as attendu ton tour.
+narrateur|Un petit oiseau jaune apparaît.
+narrateur|La craie laisse une poussière sur le bois.
+narrateur|On est encore à la table.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10007,7 +10572,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10175,7 +10740,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10203,7 +10771,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, à la table. La poupée a un nuage dessiné au dos. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10343,7 +10911,22 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, à la table.
+narrateur|La poupée a un nuage dessiné au dos.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10371,7 +10954,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, à la table. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10511,7 +11094,14 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, à la table.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10539,7 +11129,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, à la table. L'ours a de la poussière jaune au museau. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10679,7 +11269,22 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, à la table.
+narrateur|L'ours a de la poussière jaune au museau.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10707,7 +11312,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, à la table. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10847,7 +11452,14 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, à la table.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10875,7 +11487,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, à la table. Le lion regarde l'oiseau du carton. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11015,7 +11627,22 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la table, pendant le dessin.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, à la table.
+narrateur|Le lion regarde l'oiseau du carton.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11043,7 +11670,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, à la table. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11183,7 +11810,14 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, à la table.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11211,7 +11845,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, Iris lève la main. Elle attend. Puis elle parle. Je vois un oiseau.</t>
+          <t>Victorina s'approche de la fenêtre. La pluie tapote la vitre, tout fin. Un oiseau jaune tient le rebord. Ses plumes sont mouillées, tout collées. Moi, je raconte la pluie. Maman parle jusqu'au bout. Victorina lève la main. Elle attend. Il penche la tête. C'est ton tour. On a attendu. Puis on parle. Bravo. Tu as levé la main. Une goutte glisse, toute lente. L'oiseau reste, tout calme.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11351,11 +11985,29 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Près de la fenêtre, Iris lève la main. Elle attend. Puis elle parle.
-narrateur|Je vois un oiseau.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Victorina s'approche de la fenêtre.
+narrateur|La pluie tapote la vitre, tout fin.
+narrateur|Un oiseau jaune tient le rebord.
+narrateur|Ses plumes sont mouillées, tout collées.
+maman|Moi, je raconte la pluie.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Il penche la tête.
+papa|C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+maman|Bravo.
+maman|Tu as levé la main.
+narrateur|Une goutte glisse, toute lente.
+narrateur|L'oiseau reste, tout calme.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>pluie,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11380,7 +12032,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, que fait Iris d'abord ?</t>
+          <t>Près de la fenêtre, chacun son tour. On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11536,7 +12188,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Près de la fenêtre, que fait Iris d'abord ?</t>
+          <t>narrateur|Près de la fenêtre, chacun son tour.
+maman|On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11564,7 +12217,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Victorina hoche la tête. Chacun son tour. On continue, tout doux. Tu as levé la main.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11708,7 +12361,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Iris a levé la main. Elle a attendu. Puis elle a parlé.</t>
+          <t>maman|Oui.
+maman|On lève la main.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Victorina hoche la tête.
+enfant-f|Chacun son tour.
+papa|On continue, tout doux.
+papa|Tu as levé la main.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11736,7 +12396,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>La petite classe a trois jeux. L'histoire, la chanson, ou le dessin ? On écoute. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11900,7 +12560,11 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre l'histoire, la chanson, ou le dessin.</t>
+          <t>narrateur|La petite classe a trois jeux.
+maman|L'histoire, la chanson, ou le dessin ?
+papa|On écoute.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11928,7 +12592,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Près de la fenêtre, l'histoire. Iris attend. Puis elle parle.</t>
+          <t>Maman ouvre un livre d'images. Une page sent le papier, un peu sec. Un oiseau y est dessiné, tout jaune. Moi, je lis l'histoire d'abord. Maman lit jusqu'au bout. Victorina lève la main. Elle attend. C'est ton tour. Le mien est dehors, sur le rebord. Oui. Merci d'avoir attendu. On attend. Puis on parle. Victorina pose un doigt sur l'image. L'oiseau vrai regarde l'oiseau du livre. On est encore près de la fenêtre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12068,10 +12732,30 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Près de la fenêtre, l'histoire. Iris attend. Puis elle parle.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Maman ouvre un livre d'images.
+narrateur|Une page sent le papier, un peu sec.
+narrateur|Un oiseau y est dessiné, tout jaune.
+maman|Moi, je lis l'histoire d'abord.
+narrateur|Maman lit jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+papa|C'est ton tour.
+enfant-f|Le mien est dehors, sur le rebord.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Victorina pose un doigt sur l'image.
+narrateur|L'oiseau vrai regarde l'oiseau du livre.
+narrateur|On est encore près de la fenêtre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12096,7 +12780,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12948,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12292,7 +12979,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, près de la fenêtre. La poupée regarde l'oiseau, tout près. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12432,7 +13119,22 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, près de la fenêtre.
+narrateur|La poupée regarde l'oiseau, tout près.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12460,7 +13162,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, près de la fenêtre. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12600,7 +13302,14 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, près de la fenêtre.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12628,7 +13337,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, près de la fenêtre. L'ours est chaud contre la vitre froide. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12768,7 +13477,22 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, près de la fenêtre.
+narrateur|L'ours est chaud contre la vitre froide.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12796,7 +13520,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, près de la fenêtre. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12936,7 +13660,14 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, près de la fenêtre.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12964,7 +13695,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, près de la fenêtre. Le lion suit l'oiseau des yeux. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13104,7 +13835,22 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant l'histoire.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, près de la fenêtre.
+narrateur|Le lion suit l'oiseau des yeux.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13132,7 +13878,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu l'histoire, près de la fenêtre. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13272,7 +14018,14 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu l'histoire, près de la fenêtre.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13300,7 +14053,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>On chante près de la lumière. Iris attend. Puis elle parle.</t>
+          <t>Papa tapote la table, tout léger. Une chanson de pluie commence. Les gouttes suivent le rythme, dehors. Moi, je chante d'abord. Papa chante jusqu'au bout. Victorina lève la main. Elle attend. Je peux chanter l'oiseau ? Oui. C'est ton tour. On a attendu. Puis on parle. Victorina chante tout bas, tout doux. Bravo, Victorina. La pluie tapote, comme un refrain. On est encore près de la fenêtre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13440,7 +14193,23 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|On chante près de la lumière. Iris attend. Puis elle parle.</t>
+          <t>narrateur|Papa tapote la table, tout léger.
+narrateur|Une chanson de pluie commence.
+narrateur|Les gouttes suivent le rythme, dehors.
+papa|Moi, je chante d'abord.
+narrateur|Papa chante jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Je peux chanter l'oiseau ?
+maman|Oui. C'est ton tour.
+maman|On a attendu.
+maman|Puis on parle.
+narrateur|Victorina chante tout bas, tout doux.
+papa|Bravo, Victorina.
+narrateur|La pluie tapote, comme un refrain.
+narrateur|On est encore près de la fenêtre.
+maman|On attend.
+maman|Puis on parle.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13468,7 +14237,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13636,7 +14405,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13664,7 +14436,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, près de la fenêtre. La poupée écoute la pluie, et la chanson. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13804,7 +14576,22 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, près de la fenêtre.
+narrateur|La poupée écoute la pluie, et la chanson.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13832,7 +14619,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, près de la fenêtre. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13972,7 +14759,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, près de la fenêtre.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14000,7 +14794,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, près de la fenêtre. L'ours a une goutte sur le nez, tout petite. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14140,7 +14934,22 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, près de la fenêtre.
+narrateur|L'ours a une goutte sur le nez, tout petite.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14168,7 +14977,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, près de la fenêtre. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14308,7 +15117,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, près de la fenêtre.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14336,7 +15152,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, près de la fenêtre. La crinière frôle la vitre, tout léger. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14476,7 +15292,22 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant la chanson.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, près de la fenêtre.
+narrateur|La crinière frôle la vitre, tout léger.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14504,7 +15335,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu la chanson, près de la fenêtre. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14644,7 +15475,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu la chanson, près de la fenêtre.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14672,7 +15510,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Iris dessine la fenêtre. Elle attend. Puis elle parle.</t>
+          <t>Victorina prend un morceau de craie. La craie est jaune, un peu cassée. Elle fait un bruit rêche sur le carton. Moi, je dessine d'abord un nuage. Maman dessine jusqu'au bout. Victorina lève la main. Elle attend. Un bec, et deux pattes ? Oui. C'est ton tour. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Un petit oiseau jaune apparaît. Le trait jaune copie l'oiseau du rebord. On est encore près de la fenêtre. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14812,10 +15650,31 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Iris dessine la fenêtre. Elle attend. Puis elle parle.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Victorina prend un morceau de craie.
+narrateur|La craie est jaune, un peu cassée.
+narrateur|Elle fait un bruit rêche sur le carton.
+maman|Moi, je dessine d'abord un nuage.
+narrateur|Maman dessine jusqu'au bout.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Un bec, et deux pattes ?
+papa|Oui. C'est ton tour.
+papa|On attend.
+papa|Puis on parle.
+maman|Bravo.
+maman|Tu as attendu ton tour.
+narrateur|Un petit oiseau jaune apparaît.
+narrateur|Le trait jaune copie l'oiseau du rebord.
+narrateur|On est encore près de la fenêtre.
+maman|On attend.
+maman|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>craie</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14840,7 +15699,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Léa, Tom, ou Sami.</t>
+          <t>Qui écoute, tout près ? La poupée, l'ours, ou le lion ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15008,7 +15867,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
+          <t>narrateur|Qui écoute, tout près ?
+papa|La poupée, l'ours, ou le lion ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15036,7 +15898,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>La poupée est assise, tout droite. Sa robe de toile est un peu froissée. Un bouton brille, tout petit. Victorina a encore la poupée, près de la fenêtre. La poupée a un oiseau jaune sur la robe. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15176,7 +16038,22 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Léa. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>narrateur|La poupée est assise, tout droite.
+narrateur|Sa robe de toile est un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Victorina a encore la poupée, près de la fenêtre.
+narrateur|La poupée a un oiseau jaune sur la robe.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose la poupée tout près.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15204,7 +16081,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, près de la fenêtre. Elle a parlé avec la poupée. Bravo, Victorina. C'est du bon travail. La poupée reste assise, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15344,7 +16221,14 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, près de la fenêtre.
+narrateur|Elle a parlé avec la poupée.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|La poupée reste assise, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15372,7 +16256,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Il sent encore le placard. Victorina a encore l'ours, près de la fenêtre. L'ours compare le dessin et l'oiseau vrai. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15512,7 +16396,22 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Tom. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Il sent encore le placard.
+narrateur|Victorina a encore l'ours, près de la fenêtre.
+narrateur|L'ours compare le dessin et l'oiseau vrai.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose l'ours tout près.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15540,7 +16439,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, près de la fenêtre. Elle a parlé avec l'ours. Bravo, Victorina. C'est du bon travail. L'ours referme une oreille, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15680,7 +16579,14 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, près de la fenêtre.
+narrateur|Elle a parlé avec l'ours.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|L'ours referme une oreille, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15708,7 +16614,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>Le lion a une crinière en laine. La laine est mêlée, tout douce. Un œil de bouton regarde, tout calme. Victorina a encore le lion, près de la fenêtre. Le lion a un bec jaune, en craie, au museau. On dit bonjour, chacun son tour. Victorina lève la main. Elle attend. Bonjour. J'ai vu l'oiseau. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans la petite classe. Merci, papa. Merci, maman. Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15848,7 +16754,22 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Iris rejoint Sami. Elle a attendu. Puis elle a parlé, à la fenêtre, pendant le dessin.</t>
+          <t>narrateur|Le lion a une crinière en laine.
+narrateur|La laine est mêlée, tout douce.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Victorina a encore le lion, près de la fenêtre.
+narrateur|Le lion a un bec jaune, en craie, au museau.
+papa|On dit bonjour, chacun son tour.
+narrateur|Victorina lève la main.
+narrateur|Elle attend.
+enfant-f|Bonjour. J'ai vu l'oiseau.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans la petite classe.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Victorina pose le lion tout près.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15876,7 +16797,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Victorina a vécu le dessin, près de la fenêtre. Elle a parlé avec le lion. Bravo, Victorina. C'est du bon travail. Le lion garde sa crinière, tout douce. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16016,7 +16937,14 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Victorina a vécu le dessin, près de la fenêtre.
+narrateur|Elle a parlé avec le lion.
+papa|Bravo, Victorina.
+papa|C'est du bon travail.
+narrateur|Le lion garde sa crinière, tout douce.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16038,7 +16966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16132,6 +17060,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-016.xlsx
+++ b/stories/arbres/TREE-COL-016.xlsx
@@ -3090,17 +3090,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Victorina installe l'ours brun sur ses genoux. L'ours est lourd, et sent le placard. On fait comme la dernière page, on ne bouge pas. Maman ferme le livre, sans le claquer. Le temps passe, un peu trop long pour les pieds. Victorina ouvre la bouche, puis la referme. Regarde, il a trouvé l'angle sec tout seul. L'oiseau se secoue au-dessus du tapis, derrière le verre. Votre silence lui a laissé de la place.</t>
+          <t>Victorina installe l'ours brun sur ses genoux. L'ours est lourd, et sent le placard. On fait comme la dernière page, on ne bouge pas. Maman ferme le livre, sans le claquer. Le temps passe, un peu trop long pour les pieds. Victorina ouvre la bouche, puis la referme. Regarde, il a trouvé l'angle sec tout seul. L'oiseau se secoue au-dessus du tapis, derrière le verre. Ce silence lui a laissé de la place.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorina installe &lt;emphasis level="moderate"&gt;l'ours&lt;/emphasis&gt; brun sur ses genoux. L'ours est lourd, et sent le placard. On fait comme la dernière page, on ne bouge pas. Maman ferme le livre, sans le claquer. Le temps passe, un peu trop long pour les pieds. Victorina ouvre la bouche, puis la referme. Regarde, il a trouvé l'angle sec tout seul. L'oiseau se secoue au-dessus du tapis, derrière le verre. Votre silence lui a laissé de la place.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Victorina installe &lt;emphasis level="moderate"&gt;l'ours&lt;/emphasis&gt; brun sur ses genoux. L'ours est lourd, et sent le placard. On fait comme la dernière page, on ne bouge pas. Maman ferme le livre, sans le claquer. Le temps passe, un peu trop long pour les pieds. Victorina ouvre la bouche, puis la referme. Regarde, il a trouvé l'angle sec tout seul. L'oiseau se secoue au-dessus du tapis, derrière le verre. Ce silence lui a laissé de la place.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Victorina installe &lt;emphasis&gt;l'ours&lt;/emphasis&gt; brun sur ses genoux. L'ours est lourd, et sent le placard. On fait comme la dernière page, on ne bouge pas. Maman ferme le livre, sans le claquer. Le temps passe, un peu trop long pour les pieds. Victorina ouvre la bouche, puis la referme. Regarde, il a trouvé l'angle sec tout seul. L'oiseau se secoue au-dessus du tapis, derrière le verre. Votre silence lui a laissé de la place. [pause]</t>
+          <t>Victorina installe &lt;emphasis&gt;l'ours&lt;/emphasis&gt; brun sur ses genoux. L'ours est lourd, et sent le placard. On fait comme la dernière page, on ne bouge pas. Maman ferme le livre, sans le claquer. Le temps passe, un peu trop long pour les pieds. Victorina ouvre la bouche, puis la referme. Regarde, il a trouvé l'angle sec tout seul. L'oiseau se secoue au-dessus du tapis, derrière le verre. Ce silence lui a laissé de la place. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3242,7 +3242,7 @@
 narrateur|Victorina ouvre la bouche, puis la referme.
 papa|Regarde, il a trouvé l'angle sec tout seul.
 narrateur|L'oiseau se secoue au-dessus du tapis, derrière le verre.
-maman|Votre silence lui a laissé de la place.</t>
+maman|Ce silence lui a laissé de la place.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -13483,17 +13483,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>L'ours est chaud contre le verre froid. Victorina s'accroupit, le livre fermé sur ses genoux. On ne parle plus, on le laisse choisir. L'oiseau quitte le filet d'eau, pas à pas. Il se secoue si près que la vitre s'embue. On n'a rien forcé, et il a trouvé. L'ours garde une petite buée sur le nez.</t>
+          <t>L'ours est chaud contre le verre froid. Victorina s'accroupit, le livre fermé sur ses genoux. On ne parle plus, on le laisse choisir. L'oiseau quitte le filet d'eau, pas à pas. Il se secoue si près que la vitre s'embue. On a attendu, et il a trouvé son angle. L'ours garde une petite buée sur le nez.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'ours est chaud contre le verre froid. Victorina s'accroupit, le livre fermé sur ses genoux. On ne parle plus, on le laisse choisir. L'oiseau quitte le filet d'eau, pas à pas. Il se secoue si près que la vitre s'embue. On n'a rien forcé, et il a trouvé. L'ours garde une petite buée sur le nez.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'ours est chaud contre le verre froid. Victorina s'accroupit, le livre fermé sur ses genoux. On ne parle plus, on le laisse choisir. L'oiseau quitte le filet d'eau, pas à pas. Il se secoue si près que la vitre s'embue. On a attendu, et il a trouvé son angle. L'ours garde une petite buée sur le nez.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>L'ours est chaud contre le verre froid. Victorina s'accroupit, le livre fermé sur ses genoux. On ne parle plus, on le laisse choisir. L'oiseau quitte le filet d'eau, pas à pas. Il se secoue si près que la vitre s'embue. On n'a rien forcé, et il a trouvé. L'ours garde une petite buée sur le nez. [pause]</t>
+          <t>L'ours est chaud contre le verre froid. Victorina s'accroupit, le livre fermé sur ses genoux. On ne parle plus, on le laisse choisir. L'oiseau quitte le filet d'eau, pas à pas. Il se secoue si près que la vitre s'embue. On a attendu, et il a trouvé son angle. L'ours garde une petite buée sur le nez. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13632,7 +13632,7 @@
 enfant-f|On ne parle plus, on le laisse choisir.
 narrateur|L'oiseau quitte le filet d'eau, pas à pas.
 narrateur|Il se secoue si près que la vitre s'embue.
-papa|On n'a rien forcé, et il a trouvé.
+papa|On a attendu, et il a trouvé son angle.
 narrateur|L'ours garde une petite buée sur le nez.</t>
         </is>
       </c>
@@ -14215,17 +14215,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Face à la vitre, papa chante tout bas. Les gouttes suivent, puis se taisent. Je veux le refrain maintenant ! Sa voix recouvre le dernier mot de papa. L'oiseau recule d'un pas, méfiant. Laisse-moi finir, ensuite c'est toi. Victorina serre ses poings, puis les ouvre. Elle attend le point, et elle pose sa note. L'oiseau avance, et glisse un cri dans le trou. Il chante avec vous, chacun son trou. On ne lui marche plus sur le bec.</t>
+          <t>Face à la vitre, papa chante tout bas. Les gouttes suivent, puis se taisent. Je veux le refrain maintenant ! Sa voix recouvre le dernier mot de papa. L'oiseau recule d'un pas, méfiant. Laisse-moi finir, ensuite c'est toi. Victorina serre ses poings, puis les ouvre. Elle attend le point, et elle pose sa note. L'oiseau avance, et glisse un cri dans le trou. Il chante avec vous, chacun son trou. Cette fois, on lui laisse son cri.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Face à la vitre, papa chante tout bas. Les gouttes suivent, puis se taisent. Je veux le refrain maintenant ! Sa voix recouvre le dernier mot de papa. L'&lt;emphasis level="moderate"&gt;oiseau&lt;/emphasis&gt; recule d'un pas, méfiant. Laisse-moi finir, ensuite c'est toi. Victorina serre ses poings, puis les ouvre. Elle attend le point, et elle pose sa note. L'oiseau avance, et glisse un cri dans le trou. Il chante avec vous, chacun son trou. On ne lui marche plus sur le bec.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Face à la vitre, papa chante tout bas. Les gouttes suivent, puis se taisent. Je veux le refrain maintenant ! Sa voix recouvre le dernier mot de papa. L'&lt;emphasis level="moderate"&gt;oiseau&lt;/emphasis&gt; recule d'un pas, méfiant. Laisse-moi finir, ensuite c'est toi. Victorina serre ses poings, puis les ouvre. Elle attend le point, et elle pose sa note. L'oiseau avance, et glisse un cri dans le trou. Il chante avec vous, chacun son trou. Cette fois, on lui laisse son cri.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Face à la vitre, papa chante tout bas. Les gouttes suivent, puis se taisent. Je veux le refrain maintenant ! Sa voix recouvre le dernier mot de papa. L'&lt;emphasis&gt;oiseau&lt;/emphasis&gt; recule d'un pas, méfiant. Laisse-moi finir, ensuite c'est toi. Victorina serre ses poings, puis les ouvre. Elle attend le point, et elle pose sa note. L'oiseau avance, et glisse un cri dans le trou. Il chante avec vous, chacun son trou. On ne lui marche plus sur le bec.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Face à la vitre, papa chante tout bas. Les gouttes suivent, puis se taisent. Je veux le refrain maintenant ! Sa voix recouvre le dernier mot de papa. L'&lt;emphasis&gt;oiseau&lt;/emphasis&gt; recule d'un pas, méfiant. Laisse-moi finir, ensuite c'est toi. Victorina serre ses poings, puis les ouvre. Elle attend le point, et elle pose sa note. L'oiseau avance, et glisse un cri dans le trou. Il chante avec vous, chacun son trou. Cette fois, on lui laisse son cri.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -14373,7 +14373,7 @@
 narrateur|Elle attend le point, et elle pose sa note.
 narrateur|L'oiseau avance, et glisse un cri dans le trou.
 maman|Il chante avec vous, chacun son trou.
-enfant-f|On ne lui marche plus sur le bec.</t>
+enfant-f|Cette fois, on lui laisse son cri.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -17177,7 +17177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17290,6 +17290,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
